--- a/Realistic_ER_Estimate/NTu/aggregate_Mumberes_results.xlsx
+++ b/Realistic_ER_Estimate/NTu/aggregate_Mumberes_results.xlsx
@@ -425,342 +425,854 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B42"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Maize</t>
+          <t>Maize - SOC Baseline (tCO2e/ha)</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Potato</t>
+          <t>Maize - SOC Project (tCO2e/ha)</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Maize - ERs (tCO2e/ha)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Potato - SOC Baseline (tCO2e/ha)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Potato - SOC Project (tCO2e/ha)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Potato - ERs (tCO2e/ha)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
+      <c r="A2" t="n">
+        <v>416.7166577479397</v>
+      </c>
+      <c r="B2" t="n">
+        <v>416.7161654532999</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="n">
+        <v>416.7166577479397</v>
+      </c>
+      <c r="E2" t="n">
+        <v>416.7161654532999</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
+        <v>357.8210322969839</v>
+      </c>
+      <c r="B3" t="n">
+        <v>416.7161622645597</v>
+      </c>
+      <c r="C3" t="n">
         <v>58.89562226221574</v>
       </c>
-      <c r="B3" t="n">
+      <c r="D3" t="n">
+        <v>350.811878400596</v>
+      </c>
+      <c r="E3" t="n">
+        <v>416.7161622645597</v>
+      </c>
+      <c r="F3" t="n">
         <v>65.9047761586036</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
+        <v>326.8695569716918</v>
+      </c>
+      <c r="B4" t="n">
+        <v>416.7161593602667</v>
+      </c>
+      <c r="C4" t="n">
         <v>30.95147242099888</v>
       </c>
-      <c r="B4" t="n">
+      <c r="D4" t="n">
+        <v>316.1460333601257</v>
+      </c>
+      <c r="E4" t="n">
+        <v>416.7161593602667</v>
+      </c>
+      <c r="F4" t="n">
         <v>34.66584213617714</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
+        <v>307.4279760269753</v>
+      </c>
+      <c r="B5" t="n">
+        <v>416.7161567150468</v>
+      </c>
+      <c r="C5" t="n">
         <v>19.44157829949677</v>
       </c>
-      <c r="B5" t="n">
+      <c r="D5" t="n">
+        <v>294.3229905268875</v>
+      </c>
+      <c r="E5" t="n">
+        <v>416.7161567150468</v>
+      </c>
+      <c r="F5" t="n">
         <v>21.82304018801844</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
+        <v>294.137422729559</v>
+      </c>
+      <c r="B6" t="n">
+        <v>416.71615430579</v>
+      </c>
+      <c r="C6" t="n">
         <v>13.29055088815939</v>
       </c>
-      <c r="B6" t="n">
+      <c r="D6" t="n">
+        <v>279.3451955783464</v>
+      </c>
+      <c r="E6" t="n">
+        <v>416.71615430579</v>
+      </c>
+      <c r="F6" t="n">
         <v>14.97779253928425</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
+        <v>284.2236496238992</v>
+      </c>
+      <c r="B7" t="n">
+        <v>416.7161521114476</v>
+      </c>
+      <c r="C7" t="n">
         <v>9.913770911317377</v>
       </c>
-      <c r="B7" t="n">
+      <c r="D7" t="n">
+        <v>268.1101074837495</v>
+      </c>
+      <c r="E7" t="n">
+        <v>416.7161521114476</v>
+      </c>
+      <c r="F7" t="n">
         <v>11.23508590025441</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
+        <v>276.2331180996159</v>
+      </c>
+      <c r="B8" t="n">
+        <v>416.7161501128483</v>
+      </c>
+      <c r="C8" t="n">
         <v>7.990529525684082</v>
       </c>
-      <c r="B8" t="n">
+      <c r="D8" t="n">
+        <v>258.9941744800695</v>
+      </c>
+      <c r="E8" t="n">
+        <v>416.7161501128483</v>
+      </c>
+      <c r="F8" t="n">
         <v>9.115931005080762</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
+        <v>269.396577754852</v>
+      </c>
+      <c r="B9" t="n">
+        <v>416.7161482925313</v>
+      </c>
+      <c r="C9" t="n">
         <v>6.836538524446823</v>
       </c>
-      <c r="B9" t="n">
+      <c r="D9" t="n">
+        <v>251.1398467741515</v>
+      </c>
+      <c r="E9" t="n">
+        <v>416.7161482925313</v>
+      </c>
+      <c r="F9" t="n">
         <v>7.854325885601004</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
+        <v>263.3023185375575</v>
+      </c>
+      <c r="B10" t="n">
+        <v>416.716146634593</v>
+      </c>
+      <c r="C10" t="n">
         <v>6.094257559356332</v>
       </c>
-      <c r="B10" t="n">
+      <c r="D10" t="n">
+        <v>244.0895864638945</v>
+      </c>
+      <c r="E10" t="n">
+        <v>416.716146634593</v>
+      </c>
+      <c r="F10" t="n">
         <v>7.050258652318742</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
+        <v>257.7264799297763</v>
+      </c>
+      <c r="B11" t="n">
+        <v>416.7161451245489</v>
+      </c>
+      <c r="C11" t="n">
         <v>5.575837097736961</v>
       </c>
-      <c r="B11" t="n">
+      <c r="D11" t="n">
+        <v>237.5958517398772</v>
+      </c>
+      <c r="E11" t="n">
+        <v>416.7161451245489</v>
+      </c>
+      <c r="F11" t="n">
         <v>6.493733213973139</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
+        <v>252.5443342103936</v>
+      </c>
+      <c r="B12" t="n">
+        <v>416.7161437492061</v>
+      </c>
+      <c r="C12" t="n">
         <v>5.182144344040002</v>
       </c>
-      <c r="B12" t="n">
+      <c r="D12" t="n">
+        <v>231.521790766261</v>
+      </c>
+      <c r="E12" t="n">
+        <v>416.7161437492061</v>
+      </c>
+      <c r="F12" t="n">
         <v>6.07405959827345</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
+        <v>247.6837187973068</v>
+      </c>
+      <c r="B13" t="n">
+        <v>416.7161424965486</v>
+      </c>
+      <c r="C13" t="n">
         <v>4.860614160429283</v>
       </c>
-      <c r="B13" t="n">
+      <c r="D13" t="n">
+        <v>225.7891394114976</v>
+      </c>
+      <c r="E13" t="n">
+        <v>416.7161424965486</v>
+      </c>
+      <c r="F13" t="n">
         <v>5.732650102105995</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
+        <v>243.1005292397039</v>
+      </c>
+      <c r="B14" t="n">
+        <v>416.7161413556326</v>
+      </c>
+      <c r="C14" t="n">
         <v>4.583188416686866</v>
       </c>
-      <c r="B14" t="n">
+      <c r="D14" t="n">
+        <v>220.3508172245535</v>
+      </c>
+      <c r="E14" t="n">
+        <v>416.7161413556326</v>
+      </c>
+      <c r="F14" t="n">
         <v>5.438321046028006</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
+        <v>238.7657955054143</v>
+      </c>
+      <c r="B15" t="n">
+        <v>416.7161403164905</v>
+      </c>
+      <c r="C15" t="n">
         <v>4.334732695147475</v>
       </c>
-      <c r="B15" t="n">
+      <c r="D15" t="n">
+        <v>215.1764868429656</v>
+      </c>
+      <c r="E15" t="n">
+        <v>416.7161403164905</v>
+      </c>
+      <c r="F15" t="n">
         <v>5.174329342445771</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
+        <v>234.6588519389016</v>
+      </c>
+      <c r="B16" t="n">
+        <v>416.7161393700435</v>
+      </c>
+      <c r="C16" t="n">
         <v>4.106942620065733</v>
       </c>
-      <c r="B16" t="n">
+      <c r="D16" t="n">
+        <v>210.2449303203786</v>
+      </c>
+      <c r="E16" t="n">
+        <v>416.7161393700435</v>
+      </c>
+      <c r="F16" t="n">
         <v>4.931555576140039</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
+        <v>230.7637170252755</v>
+      </c>
+      <c r="B17" t="n">
+        <v>416.7161385080228</v>
+      </c>
+      <c r="C17" t="n">
         <v>3.895134051605346</v>
       </c>
-      <c r="B17" t="n">
+      <c r="D17" t="n">
+        <v>205.5400145462537</v>
+      </c>
+      <c r="E17" t="n">
+        <v>416.7161385080228</v>
+      </c>
+      <c r="F17" t="n">
         <v>4.704914912104106</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
+        <v>227.0671656339193</v>
+      </c>
+      <c r="B18" t="n">
+        <v>416.7161377228974</v>
+      </c>
+      <c r="C18" t="n">
         <v>3.696550606230898</v>
       </c>
-      <c r="B18" t="n">
+      <c r="D18" t="n">
+        <v>201.0485480846964</v>
+      </c>
+      <c r="E18" t="n">
+        <v>416.7161377228974</v>
+      </c>
+      <c r="F18" t="n">
         <v>4.491465676431979</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
+        <v>223.5576946412129</v>
+      </c>
+      <c r="B19" t="n">
+        <v>416.7161370078083</v>
+      </c>
+      <c r="C19" t="n">
         <v>3.509470277617171</v>
       </c>
-      <c r="B19" t="n">
+      <c r="D19" t="n">
+        <v>196.7591357026538</v>
+      </c>
+      <c r="E19" t="n">
+        <v>416.7161370078083</v>
+      </c>
+      <c r="F19" t="n">
         <v>4.289411666953401</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
+        <v>220.2249608035178</v>
+      </c>
+      <c r="B20" t="n">
+        <v>416.7161363565076</v>
+      </c>
+      <c r="C20" t="n">
         <v>3.33273318639454</v>
       </c>
-      <c r="B20" t="n">
+      <c r="D20" t="n">
+        <v>192.6615597873316</v>
+      </c>
+      <c r="E20" t="n">
+        <v>416.7161363565076</v>
+      </c>
+      <c r="F20" t="n">
         <v>4.097575264021653</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
+        <v>217.0594688189303</v>
+      </c>
+      <c r="B21" t="n">
+        <v>416.7161357633055</v>
+      </c>
+      <c r="C21" t="n">
         <v>3.165491391385354</v>
       </c>
-      <c r="B21" t="n">
+      <c r="D21" t="n">
+        <v>188.7464405156993</v>
+      </c>
+      <c r="E21" t="n">
+        <v>416.7161357633055</v>
+      </c>
+      <c r="F21" t="n">
         <v>3.915118678430183</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
+        <v>214.0523924143166</v>
+      </c>
+      <c r="B22" t="n">
+        <v>416.7161352230189</v>
+      </c>
+      <c r="C22" t="n">
         <v>3.007075864327076</v>
       </c>
-      <c r="B22" t="n">
+      <c r="D22" t="n">
+        <v>185.0050439257739</v>
+      </c>
+      <c r="E22" t="n">
+        <v>416.7161352230189</v>
+      </c>
+      <c r="F22" t="n">
         <v>3.741396049638664</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
+        <v>211.1954665914397</v>
+      </c>
+      <c r="B23" t="n">
+        <v>416.7161347309275</v>
+      </c>
+      <c r="C23" t="n">
         <v>2.856925330785553</v>
       </c>
-      <c r="B23" t="n">
+      <c r="D23" t="n">
+        <v>181.4291688428006</v>
+      </c>
+      <c r="E23" t="n">
+        <v>416.7161347309275</v>
+      </c>
+      <c r="F23" t="n">
         <v>3.575874590882028</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
+        <v>208.4809183262655</v>
+      </c>
+      <c r="B24" t="n">
+        <v>416.7161342827328</v>
+      </c>
+      <c r="C24" t="n">
         <v>2.714547816979506</v>
       </c>
-      <c r="B24" t="n">
+      <c r="D24" t="n">
+        <v>178.0110761907933</v>
+      </c>
+      <c r="E24" t="n">
+        <v>416.7161342827328</v>
+      </c>
+      <c r="F24" t="n">
         <v>3.418092203812568</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
+        <v>205.9014183985857</v>
+      </c>
+      <c r="B25" t="n">
+        <v>416.7161338745187</v>
+      </c>
+      <c r="C25" t="n">
         <v>2.579499519465633</v>
       </c>
-      <c r="B25" t="n">
+      <c r="D25" t="n">
+        <v>174.7434413975393</v>
+      </c>
+      <c r="E25" t="n">
+        <v>416.7161338745187</v>
+      </c>
+      <c r="F25" t="n">
         <v>3.267634385039917</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
+        <v>203.4500451481282</v>
+      </c>
+      <c r="B26" t="n">
+        <v>416.7161335027185</v>
+      </c>
+      <c r="C26" t="n">
         <v>2.451372878657428</v>
       </c>
-      <c r="B26" t="n">
+      <c r="D26" t="n">
+        <v>171.6193196624621</v>
+      </c>
+      <c r="E26" t="n">
+        <v>416.7161335027185</v>
+      </c>
+      <c r="F26" t="n">
         <v>3.124121363277036</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
+        <v>201.1202552414602</v>
+      </c>
+      <c r="B27" t="n">
+        <v>416.7161331640843</v>
+      </c>
+      <c r="C27" t="n">
         <v>2.329789568033772</v>
       </c>
-      <c r="B27" t="n">
+      <c r="D27" t="n">
+        <v>168.6321186393714</v>
+      </c>
+      <c r="E27" t="n">
+        <v>416.7161331640843</v>
+      </c>
+      <c r="F27" t="n">
         <v>2.987200684456449</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
+        <v>198.9058588012946</v>
+      </c>
+      <c r="B28" t="n">
+        <v>416.7161328556575</v>
+      </c>
+      <c r="C28" t="n">
         <v>2.214396131738722</v>
       </c>
-      <c r="B28" t="n">
+      <c r="D28" t="n">
+        <v>165.7755756126704</v>
+      </c>
+      <c r="E28" t="n">
+        <v>416.7161328556575</v>
+      </c>
+      <c r="F28" t="n">
         <v>2.856542718274113</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
+        <v>196.8009974507182</v>
+      </c>
+      <c r="B29" t="n">
+        <v>416.7161325747434</v>
+      </c>
+      <c r="C29" t="n">
         <v>2.104861069662306</v>
       </c>
-      <c r="B29" t="n">
+      <c r="D29" t="n">
+        <v>163.0437375821793</v>
+      </c>
+      <c r="E29" t="n">
+        <v>416.7161325747434</v>
+      </c>
+      <c r="F29" t="n">
         <v>2.731837749577134</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
+        <v>194.8001244628053</v>
+      </c>
+      <c r="B30" t="n">
+        <v>416.7161323188877</v>
+      </c>
+      <c r="C30" t="n">
         <v>2.000872732057199</v>
       </c>
-      <c r="B30" t="n">
+      <c r="D30" t="n">
+        <v>160.4309433804542</v>
+      </c>
+      <c r="E30" t="n">
+        <v>416.7161323188877</v>
+      </c>
+      <c r="F30" t="n">
         <v>2.612793945869356</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
+        <v>192.8979865466064</v>
+      </c>
+      <c r="B31" t="n">
+        <v>416.7161320858555</v>
+      </c>
+      <c r="C31" t="n">
         <v>1.902137683166662</v>
       </c>
-      <c r="B31" t="n">
+      <c r="D31" t="n">
+        <v>157.9318073237266</v>
+      </c>
+      <c r="E31" t="n">
+        <v>416.7161320858555</v>
+      </c>
+      <c r="F31" t="n">
         <v>2.499135823695321</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
+        <v>191.0896069837356</v>
+      </c>
+      <c r="B32" t="n">
+        <v>416.7161318736105</v>
+      </c>
+      <c r="C32" t="n">
         <v>1.808379350625903</v>
       </c>
-      <c r="B32" t="n">
+      <c r="D32" t="n">
+        <v>155.5412040996828</v>
+      </c>
+      <c r="E32" t="n">
+        <v>416.7161318736105</v>
+      </c>
+      <c r="F32" t="n">
         <v>2.390603011798954</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
+        <v>189.3702699296777</v>
+      </c>
+      <c r="B33" t="n">
+        <v>416.7161316802985</v>
+      </c>
+      <c r="C33" t="n">
         <v>1.719336860745831</v>
       </c>
-      <c r="B33" t="n">
+      <c r="D33" t="n">
+        <v>153.2542547047254</v>
+      </c>
+      <c r="E33" t="n">
+        <v>416.7161316802985</v>
+      </c>
+      <c r="F33" t="n">
         <v>2.286949201645276</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
+        <v>187.7355057495676</v>
+      </c>
+      <c r="B34" t="n">
+        <v>416.7161315042308</v>
+      </c>
+      <c r="C34" t="n">
         <v>1.63476400404232</v>
       </c>
-      <c r="B34" t="n">
+      <c r="D34" t="n">
+        <v>151.0663133036289</v>
+      </c>
+      <c r="E34" t="n">
+        <v>416.7161315042308</v>
+      </c>
+      <c r="F34" t="n">
         <v>2.187941225028804</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
+        <v>186.1810772901766</v>
+      </c>
+      <c r="B35" t="n">
+        <v>416.7161313438687</v>
+      </c>
+      <c r="C35" t="n">
         <v>1.554428299028989</v>
       </c>
-      <c r="B35" t="n">
+      <c r="D35" t="n">
+        <v>148.9729549186053</v>
+      </c>
+      <c r="E35" t="n">
+        <v>416.7161313438687</v>
+      </c>
+      <c r="F35" t="n">
         <v>2.09335822466151</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
+        <v>184.7029670091107</v>
+      </c>
+      <c r="B36" t="n">
+        <v>416.7161311978115</v>
+      </c>
+      <c r="C36" t="n">
         <v>1.478110135008767</v>
       </c>
-      <c r="B36" t="n">
+      <c r="D36" t="n">
+        <v>146.9699638748926</v>
+      </c>
+      <c r="E36" t="n">
+        <v>416.7161311978115</v>
+      </c>
+      <c r="F36" t="n">
         <v>2.002990897655593</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
+        <v>183.2973648945673</v>
+      </c>
+      <c r="B37" t="n">
+        <v>416.7161310647832</v>
+      </c>
+      <c r="C37" t="n">
         <v>1.405601981515008</v>
       </c>
-      <c r="B37" t="n">
+      <c r="D37" t="n">
+        <v>145.0533229424797</v>
+      </c>
+      <c r="E37" t="n">
+        <v>416.7161310647832</v>
+      </c>
+      <c r="F37" t="n">
         <v>1.916640799384463</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
+        <v>181.9606571174762</v>
+      </c>
+      <c r="B38" t="n">
+        <v>416.7161309436214</v>
+      </c>
+      <c r="C38" t="n">
         <v>1.336707655929378</v>
       </c>
-      <c r="B38" t="n">
+      <c r="D38" t="n">
+        <v>143.2192031219188</v>
+      </c>
+      <c r="E38" t="n">
+        <v>416.7161309436214</v>
+      </c>
+      <c r="F38" t="n">
         <v>1.834119699399177</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
+        <v>180.6894153641231</v>
+      </c>
+      <c r="B39" t="n">
+        <v>416.716130833268</v>
+      </c>
+      <c r="C39" t="n">
         <v>1.271241642999641</v>
       </c>
-      <c r="B39" t="n">
+      <c r="D39" t="n">
+        <v>141.4639540281505</v>
+      </c>
+      <c r="E39" t="n">
+        <v>416.716130833268</v>
+      </c>
+      <c r="F39" t="n">
         <v>1.75524898341492</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
+        <v>179.4803868023034</v>
+      </c>
+      <c r="B40" t="n">
+        <v>416.7161307327582</v>
+      </c>
+      <c r="C40" t="n">
         <v>1.209028461309941</v>
       </c>
-      <c r="B40" t="n">
+      <c r="D40" t="n">
+        <v>139.784094830862</v>
+      </c>
+      <c r="E40" t="n">
+        <v>416.7161307327582</v>
+      </c>
+      <c r="F40" t="n">
         <v>1.679859096778709</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
+        <v>178.3304846381474</v>
+      </c>
+      <c r="B41" t="n">
+        <v>416.7161306412145</v>
+      </c>
+      <c r="C41" t="n">
         <v>1.149902072612292</v>
       </c>
-      <c r="B41" t="n">
+      <c r="D41" t="n">
+        <v>138.1763057136383</v>
+      </c>
+      <c r="E41" t="n">
+        <v>416.7161306412145</v>
+      </c>
+      <c r="F41" t="n">
         <v>1.607789025679996</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
+        <v>177.2367792242956</v>
+      </c>
+      <c r="B42" t="n">
+        <v>416.7161305578367</v>
+      </c>
+      <c r="C42" t="n">
         <v>1.093705330474052</v>
       </c>
-      <c r="B42" t="n">
+      <c r="D42" t="n">
+        <v>136.6374198173389</v>
+      </c>
+      <c r="E42" t="n">
+        <v>416.7161305578367</v>
+      </c>
+      <c r="F42" t="n">
         <v>1.538885812921578</v>
       </c>
     </row>
